--- a/ig/DM-OCTOBRE-2026/ValueSet-JDV-J229-ProfessionSante-ROR.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-JDV-J229-ProfessionSante-ROR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="97">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260730120000</t>
+    <t>20261102120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:00:00+01:00</t>
+    <t>2026-11-02T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -290,6 +290,18 @@
   </si>
   <si>
     <t>Stomathérapeute</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>Infirmier expert en plaies et cicatrisation</t>
+  </si>
+  <si>
+    <t>134</t>
+  </si>
+  <si>
+    <t>Sexologue</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R356-ProfessionRessource/FHIR/TRE-R356-ProfessionRessource</t>
@@ -824,7 +836,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -857,18 +869,34 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="B5" t="s" s="2">
-        <v>92</v>
+      <c r="B7" t="s" s="2">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-OCTOBRE-2026/ValueSet-JDV-J229-ProfessionSante-ROR.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-JDV-J229-ProfessionSante-ROR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="99">
   <si>
     <t>Property</t>
   </si>
@@ -281,6 +281,12 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_G15-ProfessionSante/FHIR/TRE-G15-ProfessionSante</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>Médiateur de santé pair ou de santé communautaire</t>
   </si>
   <si>
     <t>Infirmier en pratique avancée (IPA)</t>
@@ -836,7 +842,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -853,15 +859,15 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s" s="2">
         <v>91</v>
@@ -885,18 +891,26 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="B7" t="s" s="2">
-        <v>96</v>
+      <c r="B8" t="s" s="2">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
